--- a/config/_TableConfig/!tables__.xlsx
+++ b/config/_TableConfig/!tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31050" windowHeight="11380"/>
+    <workbookView windowWidth="22210" windowHeight="11510"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
   <si>
     <t>##var</t>
   </si>
@@ -123,6 +123,15 @@
   </si>
   <si>
     <t>one</t>
+  </si>
+  <si>
+    <t>Game.TbDefine</t>
+  </si>
+  <si>
+    <t>Define</t>
+  </si>
+  <si>
+    <t>Game.Define-游戏设置.xlsx</t>
   </si>
   <si>
     <t>Character.TbWeaponType</t>
@@ -1113,7 +1122,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="6.45454545454545" style="1" customWidth="1"/>
@@ -1270,7 +1279,9 @@
         <v>34</v>
       </c>
       <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
+      <c r="H5" s="6" t="s">
+        <v>31</v>
+      </c>
       <c r="I5" s="6"/>
       <c r="J5" s="10"/>
       <c r="K5" s="10"/>
@@ -1279,10 +1290,18 @@
     <row r="6" spans="1:12">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="7"/>
+      <c r="C6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>37</v>
+      </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
@@ -1296,7 +1315,7 @@
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
-      <c r="F7" s="8"/>
+      <c r="F7" s="7"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
@@ -1352,8 +1371,8 @@
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="9"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="10"/>
@@ -1367,13 +1386,27 @@
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
       <c r="F12" s="7"/>
-      <c r="G12" s="2"/>
+      <c r="G12" s="9"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
       <c r="L12" s="10"/>
     </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
